--- a/templates/校验表（新）.xlsx
+++ b/templates/校验表（新）.xlsx
@@ -559,19 +559,19 @@
       <c r="A2" s="3" t="n"/>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>存款归属表与A1411、A2411核对（本金）</t>
+          <t>A1411、2411合计表与存款归属表核对（本金）</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>存款归属表与IRP001被保险存款申报表核对</t>
+          <t>A1411、2411合计表与IRP001被保险存款申报表核对</t>
         </is>
       </c>
       <c r="D2" s="5" t="n"/>
       <c r="E2" s="6" t="n"/>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>被保险存款生成表与IRP001被保险存款申报表核对</t>
+          <t>存款归属表与IRP001被保险存款申报表核对</t>
         </is>
       </c>
       <c r="G2" s="5" t="n"/>
